--- a/data/trans_orig/IP07C02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C02-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>24372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,55%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25656</t>
+          <t>25797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>42591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61227</t>
+          <t>60212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75839</t>
+          <t>74411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24579</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36308</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>35736</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>50562</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>67065</t>
+          <t>68145</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>28969</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>35130</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>51953</t>
+          <t>51653</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37750</t>
+          <t>37591</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42276</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>56692</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>76990</t>
+          <t>76565</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>43449</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24267</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>37072</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>57394</t>
+          <t>57108</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>78224</t>
+          <t>77371</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>140579</t>
+          <t>140317</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>167289</t>
+          <t>167296</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>161542</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>188731</t>
+          <t>188347</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>309188</t>
+          <t>308857</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>349109</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>105469</t>
+          <t>106491</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>132490</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>108056</t>
+          <t>107134</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>133371</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>220219</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>259538</t>
+          <t>258693</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22263</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61021</t>
+          <t>60443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76388</t>
+          <t>75891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>32536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28936</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24319</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,47 +9315,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>57,5%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>35127</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>27105</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>41806</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>48,14%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>57,29%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>35127</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>27902</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>41836</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>48,14%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>38,24%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18055</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28161</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>40379</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>24625</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>36138</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>57675</t>
+          <t>57373</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>41624</t>
+          <t>41647</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>58405</t>
+          <t>58962</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>28845</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39164</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>44304</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>63749</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>58692</t>
+          <t>58125</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>35603</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84738</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>105066</t>
+          <t>104829</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>100975</t>
+          <t>102073</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>128628</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>152094</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>261726</t>
+          <t>260549</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>304775</t>
+          <t>301516</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>154998</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>124779</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>153192</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>287343</t>
+          <t>289336</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>329999</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>34054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38321</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47463</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43816</t>
+          <t>43528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>84787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98287</t>
+          <t>97499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42650</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>13289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53287</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21413</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>28624</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>21450</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>56134</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38889</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>57142</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77294</t>
+          <t>77989</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>25738</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>50977</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>54178</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>73296</t>
+          <t>73191</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>93370</t>
+          <t>93476</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22929</t>
+          <t>23826</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>36780</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>55791</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>75854</t>
+          <t>74785</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>198260</t>
+          <t>197602</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>199001</t>
+          <t>200208</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>229629</t>
+          <t>229570</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>405306</t>
+          <t>404043</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>447615</t>
+          <t>447020</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,39%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>132564</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>100008</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>211836</t>
+          <t>211069</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>252046</t>
+          <t>251865</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
